--- a/批量生成修改注册表bat文件/emails.xlsx
+++ b/批量生成修改注册表bat文件/emails.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\CNXIGAO13\Desktop\ABB_Production_Tools_\FAST_V2.2 - Copy\批量生成修改注册表bat文件\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{75033DFC-2557-4907-9D4E-833FCE3A27D8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1DE3E599-2227-49F8-9AA9-38E9EA3AD07C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-10800" windowWidth="21840" windowHeight="37920" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="97">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="100" uniqueCount="100">
   <si>
     <t>louis-huanran.cai@cn.abb.com</t>
   </si>
@@ -327,6 +327,16 @@
   </si>
   <si>
     <t>yin-yin.chen@cn.abb.com</t>
+  </si>
+  <si>
+    <t>dylan-qiang.lan@cn.abb.com</t>
+  </si>
+  <si>
+    <t>eric-hao.zhu@cn.abb.com</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>grace-ziyi.liu@cn.abb.com</t>
   </si>
 </sst>
 </file>
@@ -383,8 +393,8 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
   </cellXfs>
   <cellStyles count="2">
-    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="超链接" xfId="1" builtinId="8"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -662,7 +672,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:A97"/>
+  <dimension ref="A1:A100"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="41.75" customWidth="1"/>
@@ -1151,6 +1161,21 @@
     <row r="97" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A97" t="s">
         <v>96</v>
+      </c>
+    </row>
+    <row r="98" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A98" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="99" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A99" s="1" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="100" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A100" t="s">
+        <v>99</v>
       </c>
     </row>
   </sheetData>
@@ -1165,9 +1190,10 @@
     <hyperlink ref="A89" r:id="rId7" xr:uid="{7BBB6A39-8E4D-4F94-B6A8-06B378F38517}"/>
     <hyperlink ref="A94" r:id="rId8" xr:uid="{0F62294E-1AD6-47FE-A4D8-633029A78ED4}"/>
     <hyperlink ref="A95" r:id="rId9" xr:uid="{D3E4CFCA-DE0F-4FC7-98F0-FAA361C9161F}"/>
+    <hyperlink ref="A99" r:id="rId10" xr:uid="{5B9C27E7-8072-4B89-9D7D-438737BE9970}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId10"/>
+  <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId11"/>
 </worksheet>
 </file>
 
